--- a/content/tz-kak-bystro-vyuchit-kitayskiy.xlsx
+++ b/content/tz-kak-bystro-vyuchit-kitayskiy.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -679,46 +679,58 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Целевой объём блока T123</t>
+          <t>Объём блока T123</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>40 000–45 000. Вилка взята по факту: в прошлой статье вышло 45 350 при той же вилке</t>
+          <t>ПЛАН 40 000–45 000. ФАКТ 41 209 — ПЕРВОЕ ПОЛНОЕ ПОПАДАНИЕ В ВИЛКУ за пять статей</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Целевая позиция инфографики</t>
+          <t>Позиция инфографики</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>26–31 %</t>
+          <t>ПЛАН 26–31 %. ФАКТ 27,3 % (при первой сборке 32,8 %)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Целевая позиция «Из личного опыта»</t>
+          <t>Позиция «Из личного опыта»</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>36–40 %</t>
+          <t>ПЛАН 36–40 %. ФАКТ 38,3 % (при первой сборке 52,8 %)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>Позиция FAQ</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>74,2 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>Ключи и где отрабатываются</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>как быстро выучить китайский — тайтл, H1, первый абзац, раздел 3, FAQ. как быстро научиться китайскому языку — раздел 1, FAQ. как можно быстро выучить китайский — раздел 3, что действительно ускоряет. как быстро можно выучить китайский язык — раздел 4, чего ускорить нельзя, FAQ. быстро выучить китайский язык — раздел 5, честная интенсивная неделя</t>
         </is>
@@ -735,12 +747,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -778,7 +790,11 @@
           <t>40 000–45 000, лимит ≈ 50 000</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>41 209 — ПЕРВОЕ ПОЛНОЕ ПОПАДАНИЕ В ВИЛКУ за пять статей. Помогло то, что часы, сроки, плато и этапы ушли ссылками</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -791,7 +807,11 @@
           <t>26–31 %</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>27,3 %. При первой сборке 32,8 % — перенесена внутрь раздела про подмены</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -804,7 +824,11 @@
           <t>36–40 %</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>38,3 %. При первой сборке 52,8 % — перенесена в раздел про то, что ускоряет старт</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -817,7 +841,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>74,2 %</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -830,7 +858,11 @@
           <t>A = B</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>22 / 22</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -843,7 +875,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -856,7 +892,11 @@
           <t>position: sticky, top 90</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>sticky, top 90px</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -869,7 +909,11 @@
           <t>static, order 2, нет горизонтальной прокрутки</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>static, order 2, ширина документа 390</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -882,7 +926,11 @@
           <t>да</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>да: BlogPosting, Person, EducationalOrganization, FAQPage, BreadcrumbList</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -895,7 +943,11 @@
           <t>совпадение полное</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>6 вопросов и 6 ответов, совпадение полное</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -908,7 +960,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>0; ёлочек 16 пар</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -921,7 +977,11 @@
           <t>все верны</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>все восемь верны</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -934,7 +994,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>шесть найдены и исправлены: лежит число повторений, не двигает скорость, объём тает (дважды), буксует, ощущение полёта</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -947,46 +1011,79 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>0. Единственное число в тексте — HSK 1 в подписи ссылки: это название ступени, а не срок</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Высота инфографики</t>
+          <t>Правило .han в CSS</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>подбирается замером</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr"/>
+          <t>есть, с запретом переноса</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>есть, унаследовано</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Дефекты рендеров</t>
+          <t>Высота инфографики</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>0 на отдаче</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr"/>
+          <t>подбирается замером</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>452 px при содержимом до 429, запас 23</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>Дефекты рендеров</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>0 на отдаче</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>три найдены и исправлены, один потребовал сменить приём целиком. См. лист Картинки</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t>Адреса Tilda вшиты</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>7 в исходнике / 5 в блоке, assets = 0</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>ждём ссылки от заказчика</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1917,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2033,13 +2130,51 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Дефекты рендеров</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
+          <t>ДЕФЕКТ 1. Обложка</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>ПРИЁМ ПРИШЛОСЬ ЗАМЕНИТЬ ЦЕЛИКОМ: отгиб угла отрисовался неверно, треугольник налез на баннер, слово УЗНАВАНИЕ обрезалось, подпись не читалась</t>
+        </is>
+      </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>проставляется после просмотра</t>
+          <t>Отгиб угла средствами CSS надёжно не выходит. Заменено на рекламный баннер СО СНОСКОЙ ПЕТИТОМ: крупное обещание со звёздочкой, под чертой мелким шрифтом — что под словом ВЫУЧИТЬ имеется в виду узнавание. Приём столь же новый, метафора даже точнее</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ДЕФЕКТ 2. Обложка</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>разделительная черта перед сноской прошла через строку ЧИТАЕТЕ ПИНЬИНЬ</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>добавлен отступ снизу у списка</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ДЕФЕКТ 3. Инфографика</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>холст был на 1 px больше содержимого вместо 22</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>высота подобрана замером: 452 px при содержимом до 429</t>
         </is>
       </c>
     </row>

--- a/content/tz-kak-bystro-vyuchit-kitayskiy.xlsx
+++ b/content/tz-kak-bystro-vyuchit-kitayskiy.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>ПЛАН 40 000–45 000. ФАКТ 41 209 — ПЕРВОЕ ПОЛНОЕ ПОПАДАНИЕ В ВИЛКУ за пять статей</t>
+          <t>ПЛАН 40 000–45 000. ФАКТ 41 409 с адресами Tilda — ПЕРВОЕ ПОЛНОЕ ПОПАДАНИЕ В ВИЛКУ за пять статей</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>41 209 — ПЕРВОЕ ПОЛНОЕ ПОПАДАНИЕ В ВИЛКУ за пять статей. Помогло то, что часы, сроки, плато и этапы ушли ссылками</t>
+          <t>41 409 с адресами Tilda — ПЕРВОЕ ПОЛНОЕ ПОПАДАНИЕ В ВИЛКУ за пять статей. Помогло то, что часы, сроки, плато и этапы ушли ссылками</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>ждём ссылки от заказчика</t>
+          <t>7 / 5, assets = 0. ПОРЯДОК НЕ ПРОВЕРЕН, ВТОРОЙ РАЗ ПОДРЯД: Tilda обрезала оба имени до kak-bystro-vyuchit-k.png, прокси отдаёт 403. Вшито по обычному порядку. ПРЕДЛОЖЕНИЕ: называть файлы oblozhka-&lt;слаг&gt;.png и infografika-&lt;слаг&gt;.png — тогда первые 20 знаков будут различаться всегда</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>адрес обложки на static.tildacdn.com — подставляется после загрузки</t>
+          <t>https://static.tildacdn.com/tild3930-3738-4430-a462-656435383938/kak-bystro-vyuchit-k.png</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>адрес обложки на static.tildacdn.com</t>
+          <t>https://static.tildacdn.com/tild3930-3738-4430-a462-656435383938/kak-bystro-vyuchit-k.png</t>
         </is>
       </c>
     </row>
